--- a/input/Template_JENA_PTR_protection.xlsx
+++ b/input/Template_JENA_PTR_protection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acted-my.sharepoint.com/personal/martina_vit_impact-initiatives_org/Documents/PiN_app_dev/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="473" documentId="8_{D63770E9-8D5C-4F2A-BD7D-98D3C6683B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC97B823-123C-4F6D-991A-C5AB5BF52A5D}"/>
+  <xr:revisionPtr revIDLastSave="482" documentId="8_{D63770E9-8D5C-4F2A-BD7D-98D3C6683B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90B2B9AB-4B86-41EE-9BAB-3FD8BBC3C455}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
+    <workbookView xWindow="28635" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator" sheetId="3" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Admin Pcode</t>
   </si>
@@ -123,19 +123,31 @@
     <t>threshold PTR (Change it according to the context average PTR)</t>
   </si>
   <si>
-    <t>Protection indicator value -- categorical variable</t>
-  </si>
-  <si>
-    <t>Protection indicator value -- continuous / discrete numerical variable</t>
-  </si>
-  <si>
-    <t>category for categorical variable --&gt; if selected the child is in need</t>
-  </si>
-  <si>
-    <t>threshold for numerical variable --&gt; if above the child is in need</t>
-  </si>
-  <si>
     <t>school PTR</t>
+  </si>
+  <si>
+    <t>sev4 - Protection indicator value -- continuous / discrete numerical variable</t>
+  </si>
+  <si>
+    <t>sev4 - threshold for numerical variable --&gt; if above the child is in need</t>
+  </si>
+  <si>
+    <t>sev4 - Protection indicator value -- categorical variable</t>
+  </si>
+  <si>
+    <t>sev4 - category for categorical variable --&gt; if selected the child is in need</t>
+  </si>
+  <si>
+    <t>sev5 - Protection indicator value -- continuous / discrete numerical variable</t>
+  </si>
+  <si>
+    <t>sev5 - threshold for numerical variable --&gt; if above the child is in need</t>
+  </si>
+  <si>
+    <t>sev5 - Protection indicator value -- categorical variable</t>
+  </si>
+  <si>
+    <t>sev5 - category for categorical variable --&gt; if selected the child is in need</t>
   </si>
 </sst>
 </file>
@@ -609,23 +621,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17DEB9B6-621B-4484-8A08-69293BE9C3A3}">
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="2" width="14.140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" style="6" customWidth="1"/>
+    <col min="1" max="2" width="14.1328125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="11.86328125" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" customWidth="1"/>
+    <col min="6" max="6" width="21.7265625" style="6" customWidth="1"/>
     <col min="7" max="7" width="37" style="6" customWidth="1"/>
-    <col min="8" max="8" width="21.85546875" style="8" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" style="8" customWidth="1"/>
-    <col min="10" max="10" width="23.5703125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="25.140625" style="8" customWidth="1"/>
-    <col min="12" max="14" width="22.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="21.86328125" style="8" customWidth="1"/>
+    <col min="9" max="9" width="22.54296875" style="8" customWidth="1"/>
+    <col min="10" max="10" width="23.54296875" style="8" customWidth="1"/>
+    <col min="11" max="11" width="25.1328125" style="8" customWidth="1"/>
+    <col min="12" max="12" width="21.86328125" style="8" customWidth="1"/>
+    <col min="13" max="13" width="22.54296875" style="8" customWidth="1"/>
+    <col min="14" max="14" width="23.54296875" style="8" customWidth="1"/>
+    <col min="15" max="15" width="25.1328125" style="8" customWidth="1"/>
+    <col min="16" max="18" width="22.86328125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="59" x14ac:dyDescent="0.75">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -642,7 +658,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>8</v>
@@ -651,26 +667,38 @@
         <v>10</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="K1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
     </row>
   </sheetData>
   <protectedRanges>

--- a/input/Template_JENA_PTR_protection.xlsx
+++ b/input/Template_JENA_PTR_protection.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="482" documentId="8_{D63770E9-8D5C-4F2A-BD7D-98D3C6683B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90B2B9AB-4B86-41EE-9BAB-3FD8BBC3C455}"/>
   <bookViews>
-    <workbookView xWindow="28635" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator" sheetId="3" r:id="rId1"/>
@@ -622,26 +622,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17DEB9B6-621B-4484-8A08-69293BE9C3A3}">
   <dimension ref="A1:U1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.1328125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="21.7265625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11.86328125" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="6" width="21.7265625" style="6" customWidth="1"/>
+    <col min="1" max="2" width="14.140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" style="6" customWidth="1"/>
     <col min="7" max="7" width="37" style="6" customWidth="1"/>
-    <col min="8" max="8" width="21.86328125" style="8" customWidth="1"/>
-    <col min="9" max="9" width="22.54296875" style="8" customWidth="1"/>
-    <col min="10" max="10" width="23.54296875" style="8" customWidth="1"/>
-    <col min="11" max="11" width="25.1328125" style="8" customWidth="1"/>
-    <col min="12" max="12" width="21.86328125" style="8" customWidth="1"/>
-    <col min="13" max="13" width="22.54296875" style="8" customWidth="1"/>
-    <col min="14" max="14" width="23.54296875" style="8" customWidth="1"/>
-    <col min="15" max="15" width="25.1328125" style="8" customWidth="1"/>
-    <col min="16" max="18" width="22.86328125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="21.85546875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="22.5703125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="23.5703125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="21.85546875" style="8" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="23.5703125" style="8" customWidth="1"/>
+    <col min="15" max="15" width="25.140625" style="8" customWidth="1"/>
+    <col min="16" max="18" width="22.85546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="59" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
